--- a/data/trans_bre/P6901-Estudios-trans_bre.xlsx
+++ b/data/trans_bre/P6901-Estudios-trans_bre.xlsx
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-17,11; 11,06</t>
+          <t>-15,59; 11,17</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-20,47; 17,68</t>
+          <t>-19,33; 17,44</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-10,1; 26,9</t>
+          <t>-10,3; 27,54</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-51,31; 14,42</t>
+          <t>-59,26; 15,9</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-18,93; 13,21</t>
+          <t>-17,29; 13,57</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-25,48; 26,92</t>
+          <t>-23,77; 26,59</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-11,39; 40,08</t>
+          <t>-11,85; 41,21</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-58,12; 17,51</t>
+          <t>-62,77; 19,58</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-2,82; 14,9</t>
+          <t>-2,87; 14,63</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-0,16; 18,05</t>
+          <t>0,65; 18,56</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>5,16; 20,73</t>
+          <t>4,4; 19,39</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-1,48; 14,67</t>
+          <t>-1,1; 14,2</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-3,63; 20,26</t>
+          <t>-3,6; 19,95</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-0,16; 25,5</t>
+          <t>0,81; 25,81</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>6,45; 28,79</t>
+          <t>5,59; 26,48</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-1,7; 19,98</t>
+          <t>-1,32; 19,28</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-6,16; 26,62</t>
+          <t>-5,66; 28,71</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-27,75; 13,49</t>
+          <t>-28,09; 12,61</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-2,86; 31,04</t>
+          <t>-0,8; 32,22</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-0,5; 32,0</t>
+          <t>-2,1; 32,42</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-9,39; 60,52</t>
+          <t>-9,6; 67,3</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-37,04; 23,67</t>
+          <t>-38,07; 20,77</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-3,94; 64,18</t>
+          <t>-1,03; 66,73</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-0,84; 96,24</t>
+          <t>-4,58; 92,42</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-4,22; 9,7</t>
+          <t>-3,94; 9,67</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-4,56; 10,95</t>
+          <t>-3,76; 11,26</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>3,27; 17,13</t>
+          <t>3,88; 17,43</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-2,09; 13,4</t>
+          <t>-2,58; 13,15</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-5,28; 13,49</t>
+          <t>-5,03; 13,3</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-5,84; 15,48</t>
+          <t>-4,72; 16,01</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>4,17; 24,1</t>
+          <t>5,06; 24,44</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-2,77; 19,48</t>
+          <t>-3,32; 19,11</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/P6901-Estudios-trans_bre.xlsx
+++ b/data/trans_bre/P6901-Estudios-trans_bre.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>-11,55</t>
+          <t>5,17</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>-13,4%</t>
+          <t>5,97%</t>
         </is>
       </c>
     </row>
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-15,59; 11,17</t>
+          <t>-15,8; 10,43</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-19,33; 17,44</t>
+          <t>-18,27; 18,4</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-10,3; 27,54</t>
+          <t>-11,06; 26,92</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-59,26; 15,9</t>
+          <t>-7,86; 18,43</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-17,29; 13,57</t>
+          <t>-18,29; 12,45</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-23,77; 26,59</t>
+          <t>-23,35; 29,44</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-11,85; 41,21</t>
+          <t>-12,59; 39,7</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-62,77; 19,58</t>
+          <t>-8,24; 24,15</t>
         </is>
       </c>
     </row>
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>5,9</t>
+          <t>1,24</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>7,51%</t>
+          <t>1,54%</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-2,87; 14,63</t>
+          <t>-1,14; 15,82</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,65; 18,56</t>
+          <t>0,32; 17,37</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>4,4; 19,39</t>
+          <t>5,46; 20,33</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-1,1; 14,2</t>
+          <t>-5,38; 7,51</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-3,6; 19,95</t>
+          <t>-1,42; 22,0</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,81; 25,81</t>
+          <t>0,67; 24,57</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>5,59; 26,48</t>
+          <t>6,83; 27,93</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-1,32; 19,28</t>
+          <t>-6,39; 9,77</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>15,24</t>
+          <t>15,62</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>32,56%</t>
+          <t>32,31%</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-5,66; 28,71</t>
+          <t>-6,08; 27,41</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-28,09; 12,61</t>
+          <t>-28,58; 12,76</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-0,8; 32,22</t>
+          <t>-1,42; 32,47</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-2,1; 32,42</t>
+          <t>-1,07; 31,57</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-9,6; 67,3</t>
+          <t>-9,92; 63,0</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-38,07; 20,77</t>
+          <t>-37,91; 22,18</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-1,03; 66,73</t>
+          <t>-1,53; 69,47</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-4,58; 92,42</t>
+          <t>-1,96; 88,3</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>5,33</t>
+          <t>2,75</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>7,34%</t>
+          <t>3,68%</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-3,94; 9,67</t>
+          <t>-3,69; 9,74</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-3,76; 11,26</t>
+          <t>-4,68; 11,29</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>3,88; 17,43</t>
+          <t>3,16; 17,7</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-2,58; 13,15</t>
+          <t>-3,07; 8,75</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-5,03; 13,3</t>
+          <t>-4,71; 13,48</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-4,72; 16,01</t>
+          <t>-6,1; 15,72</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>5,06; 24,44</t>
+          <t>4,26; 25,11</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-3,32; 19,11</t>
+          <t>-3,96; 12,2</t>
         </is>
       </c>
     </row>
